--- a/measurements/25/Filled_2D_sections/axial/week25_axial_Batch_Allmarks.xlsx
+++ b/measurements/25/Filled_2D_sections/axial/week25_axial_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,62 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +556,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.970850684116598</v>
+        <v>2275.963718820862</v>
       </c>
       <c r="D2" t="n">
-        <v>15.03513867680619</v>
+        <v>293.5431836900257</v>
       </c>
       <c r="E2" t="n">
-        <v>10.53980565943369</v>
+        <v>205.777158112753</v>
       </c>
       <c r="F2" t="n">
         <v>1.426510047967435</v>
@@ -525,24 +575,48 @@
         <v>0.3319183006863793</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.466749237804878</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="J2" t="n">
-        <v>1.466749237804878</v>
+        <v>28.63653273809524</v>
       </c>
       <c r="K2" t="n">
-        <v>1.466749237804878</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>10.76497395833333</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>28.63653273809524</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6.019345238095238</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5.546875</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>5.920032718619869</v>
+      <c r="Y2" s="2" t="n">
+        <v>2256.592970521542</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +627,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.049672813801309</v>
+        <v>2306.009070294785</v>
       </c>
       <c r="D3" t="n">
-        <v>14.99717894414576</v>
+        <v>292.8020650999886</v>
       </c>
       <c r="E3" t="n">
-        <v>10.69206514881878</v>
+        <v>208.7498433817001</v>
       </c>
       <c r="F3" t="n">
         <v>1.40264567559267</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3380045950183355</v>
+        <v>0.3380045950183356</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.417778201219512</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="J3" t="n">
-        <v>1.417778201219512</v>
+        <v>27.68043154761905</v>
       </c>
       <c r="K3" t="n">
-        <v>1.417778201219512</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>10.60221354166667</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>27.68043154761905</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5.95610119047619</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5.915178571428571</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>12.07299753892713</v>
+      <c r="Y3" s="2" t="n">
+        <v>235.7109043314343</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +698,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.08863771564545</v>
+        <v>2320.861678004535</v>
       </c>
       <c r="D4" t="n">
-        <v>15.01146641882455</v>
+        <v>293.0810110341935</v>
       </c>
       <c r="E4" t="n">
-        <v>10.81228302746284</v>
+        <v>211.0969543457031</v>
       </c>
       <c r="F4" t="n">
         <v>1.388371575244184</v>
@@ -619,24 +717,48 @@
         <v>0.3395343827851363</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.367854420731707</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="J4" t="n">
-        <v>1.367854420731707</v>
+        <v>26.70572916666666</v>
       </c>
       <c r="K4" t="n">
-        <v>1.367854420731707</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>10.32366071428571</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>26.70572916666666</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5.894717261904762</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5.837053571428571</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>10.32194118848661</v>
+      <c r="Y4" s="2" t="n">
+        <v>201.5236136799767</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +769,66 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6.067519333729923</v>
+        <v>2312.81179138322</v>
       </c>
       <c r="D5" t="n">
-        <v>14.83900135028653</v>
+        <v>289.7138358865465</v>
       </c>
       <c r="E5" t="n">
-        <v>10.79207745703255</v>
+        <v>210.7024646373022</v>
       </c>
       <c r="F5" t="n">
         <v>1.374990256451212</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3462674623349853</v>
+        <v>0.3462674623349855</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.399009146341464</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="J5" t="n">
-        <v>1.399009146341464</v>
+        <v>27.31398809523809</v>
       </c>
       <c r="K5" t="n">
-        <v>1.399009146341464</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>10.35946800595238</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>27.31398809523809</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5.639880952380952</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.626860119047619</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="Y5" s="2" t="n">
         <v>1.165002747049295</v>
       </c>
     </row>
@@ -694,17 +840,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.026769779892921</v>
+        <v>2297.278911564626</v>
       </c>
       <c r="D6" t="n">
-        <v>14.5571392047696</v>
+        <v>284.2108130455017</v>
       </c>
       <c r="E6" t="n">
-        <v>10.8004468941107</v>
+        <v>210.8658679326375</v>
       </c>
       <c r="F6" t="n">
         <v>1.347827487833615</v>
@@ -713,23 +859,47 @@
         <v>0.3573899994884083</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.41234756097561</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="J6" t="n">
-        <v>1.41234756097561</v>
+        <v>27.57440476190476</v>
       </c>
       <c r="K6" t="n">
-        <v>1.41234756097561</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>10.26088169642857</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>27.57440476190476</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.386904761904762</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.225074404761904</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="Y6" s="2" t="n">
         <v>0.5479161629528073</v>
       </c>
     </row>
@@ -741,17 +911,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.982153480071386</v>
+        <v>2280.272108843537</v>
       </c>
       <c r="D7" t="n">
-        <v>14.21220905024831</v>
+        <v>277.4764624096098</v>
       </c>
       <c r="E7" t="n">
-        <v>10.77187192730787</v>
+        <v>210.3079757236299</v>
       </c>
       <c r="F7" t="n">
         <v>1.319381547251672</v>
@@ -760,24 +930,48 @@
         <v>0.3721724670274844</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.366901676829268</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J7" t="n">
-        <v>1.366901676829268</v>
+        <v>26.68712797619047</v>
       </c>
       <c r="K7" t="n">
-        <v>1.366901676829268</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>10.08742559523809</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>26.68712797619047</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5.29203869047619</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5.03720238095238</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.65</v>
+      <c r="Y7" s="2" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +982,67 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.022010707911957</v>
+        <v>2295.464852607709</v>
       </c>
       <c r="D8" t="n">
-        <v>13.52581552179848</v>
+        <v>264.0754459017799</v>
       </c>
       <c r="E8" t="n">
-        <v>10.7861594048942</v>
+        <v>210.5869217146011</v>
       </c>
       <c r="F8" t="n">
         <v>1.253997369597669</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4136418461930512</v>
+        <v>0.413641846193051</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.273246951219512</v>
+        <v>3.809523809523809</v>
       </c>
       <c r="J8" t="n">
-        <v>1.273246951219512</v>
+        <v>24.85863095238095</v>
       </c>
       <c r="K8" t="n">
-        <v>1.273246951219512</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>9.739118303571429</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>24.85863095238095</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5.239955357142857</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5.048363095238095</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>1.079744664634146</v>
+      <c r="Y8" s="2" t="n">
+        <v>2.521298363095238</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1053,67 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.982153480071386</v>
+        <v>2280.272108843537</v>
       </c>
       <c r="D9" t="n">
-        <v>12.36835592549022</v>
+        <v>241.4774252119518</v>
       </c>
       <c r="E9" t="n">
-        <v>10.6422692886213</v>
+        <v>207.7776384921301</v>
       </c>
       <c r="F9" t="n">
         <v>1.162191595613395</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4914094074494035</v>
+        <v>0.4914094074494036</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9706554878048781</v>
+        <v>3.809523809523809</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9706554878048781</v>
+        <v>18.95089285714286</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9706554878048781</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>8.411458333333334</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>18.95089285714286</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6.114211309523809</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.771205357142857</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.079744664634146</v>
+      <c r="Y9" s="2" t="n">
+        <v>16.74562872023809</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1124,67 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.859607376561571</v>
+        <v>2233.560090702947</v>
       </c>
       <c r="D10" t="n">
-        <v>11.97811201723611</v>
+        <v>233.8583774793716</v>
       </c>
       <c r="E10" t="n">
-        <v>10.79452882161955</v>
+        <v>210.7503246125721</v>
       </c>
       <c r="F10" t="n">
         <v>1.109646582558198</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5132177172736961</v>
+        <v>0.513217717273696</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9053925304878049</v>
+        <v>3.809523809523809</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9053925304878049</v>
+        <v>17.67671130952381</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9053925304878049</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>8.141276041666666</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>17.67671130952381</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6.409970238095238</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.668898809523809</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>1.079744664634146</v>
+      <c r="Y10" s="2" t="n">
+        <v>7.243209015376983</v>
       </c>
     </row>
     <row r="11">
@@ -929,35 +1195,67 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.773349196906604</v>
+        <v>2200.680272108843</v>
       </c>
       <c r="D11" t="n">
-        <v>11.37254062222272</v>
+        <v>222.0353169100625</v>
       </c>
       <c r="E11" t="n">
-        <v>10.78615939907911</v>
+        <v>210.5869216010684</v>
       </c>
       <c r="F11" t="n">
         <v>1.054364227474115</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5609481198696938</v>
+        <v>0.560948119869694</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6860708841463415</v>
+        <v>3.809523809523809</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6860708841463415</v>
+        <v>13.39471726190476</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6860708841463415</v>
+        <v>7.066592261904762</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>13.39471726190476</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>6.370907738095238</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.691220238095238</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="12">
@@ -968,35 +1266,70 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.743604997025581</v>
+        <v>2189.342403628118</v>
       </c>
       <c r="D12" t="n">
-        <v>11.18578808772855</v>
+        <v>218.3891959985097</v>
       </c>
       <c r="E12" t="n">
-        <v>10.64818736402</v>
+        <v>207.8931818689619</v>
       </c>
       <c r="F12" t="n">
-        <v>1.050487534199961</v>
+        <v>1.05048753419996</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5768478174519616</v>
+        <v>0.5768478174519615</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6724466463414634</v>
+        <v>0.9672619047619047</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6724466463414634</v>
+        <v>13.12872023809524</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6724466463414634</v>
+        <v>5.759672619047619</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>13.12872023809524</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>6.303943452380952</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.58891369047619</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.9672619047619047</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="n">
+        <v>17.71835730820106</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1340,67 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.789411064842356</v>
+        <v>2206.802721088435</v>
       </c>
       <c r="D13" t="n">
-        <v>10.91331067899378</v>
+        <v>213.069398970831</v>
       </c>
       <c r="E13" t="n">
-        <v>10.46143481789566</v>
+        <v>204.2470607303438</v>
       </c>
       <c r="F13" t="n">
         <v>1.043194444066614</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6108452669886753</v>
+        <v>0.6108452669886751</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5639291158536586</v>
+        <v>3.809523809523809</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5639291158536586</v>
+        <v>11.01004464285714</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5639291158536586</v>
+        <v>6.316964285714286</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11.01004464285714</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>6.238839285714286</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4.209449404761904</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1411,67 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.982153480071386</v>
+        <v>2280.272108843537</v>
       </c>
       <c r="D14" t="n">
-        <v>10.70635260895985</v>
+        <v>209.0287890320732</v>
       </c>
       <c r="E14" t="n">
-        <v>10.26039479418499</v>
+        <v>200.3219936007545</v>
       </c>
       <c r="F14" t="n">
         <v>1.043464001504855</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6558195065791377</v>
+        <v>0.6558195065791379</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5342987804878049</v>
+        <v>2.40141369047619</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5342987804878049</v>
+        <v>10.43154761904762</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5342987804878049</v>
+        <v>5.238095238095238</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10.43154761904762</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4.309895833333333</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.40141369047619</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="n">
+        <v>5.518043154761904</v>
       </c>
     </row>
     <row r="15">
@@ -1085,26 +1482,67 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.052647233789411</v>
+        <v>2307.142857142857</v>
       </c>
       <c r="D15" t="n">
-        <v>10.40428489592017</v>
+        <v>203.1312765393938</v>
       </c>
       <c r="E15" t="n">
-        <v>10.06180612924622</v>
+        <v>196.4447863329025</v>
       </c>
       <c r="F15" t="n">
         <v>1.034037504030065</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7026365788206821</v>
+        <v>0.7026365788206823</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.417410714285714</v>
+      </c>
+      <c r="J15" t="n">
+        <v>9.086681547619047</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.296875</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9.086681547619047</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.636532738095238</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.046875</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.417410714285714</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="n">
+        <v>4.707496279761904</v>
       </c>
     </row>
     <row r="16">
@@ -1115,26 +1553,67 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.056811421772754</v>
+        <v>2308.730158730159</v>
       </c>
       <c r="D16" t="n">
-        <v>10.33529889874342</v>
+        <v>201.7844070707048</v>
       </c>
       <c r="E16" t="n">
-        <v>9.90954660787815</v>
+        <v>193.4721004395258</v>
       </c>
       <c r="F16" t="n">
         <v>1.042963851699007</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7125376779386169</v>
+        <v>0.712537677938617</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.279761904761905</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8.848586309523808</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.100632440476191</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>8.848586309523808</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.660714285714286</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.613467261904762</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.279761904761905</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="n">
+        <v>3.741496598639455</v>
       </c>
     </row>
     <row r="17">
@@ -1145,17 +1624,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.011005353955979</v>
+        <v>2291.269841269841</v>
       </c>
       <c r="D17" t="n">
-        <v>10.18895741497598</v>
+        <v>198.9272638161977</v>
       </c>
       <c r="E17" t="n">
-        <v>9.79769814886698</v>
+        <v>191.28839243026</v>
       </c>
       <c r="F17" t="n">
         <v>1.039933794669337</v>
@@ -1164,7 +1643,48 @@
         <v>0.7276080321005209</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.032366071428571</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8.363095238095237</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.663969494047619</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>8.363095238095237</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.616071428571428</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.644345238095238</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.032366071428571</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="18">
@@ -1175,17 +1695,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.920880428316479</v>
+        <v>2256.916099773242</v>
       </c>
       <c r="D18" t="n">
-        <v>10.00812295297297</v>
+        <v>195.3966862247104</v>
       </c>
       <c r="E18" t="n">
-        <v>9.631151155727666</v>
+        <v>188.0367606594449</v>
       </c>
       <c r="F18" t="n">
         <v>1.039140886810931</v>
@@ -1194,7 +1714,45 @@
         <v>0.742832489441156</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.236979166666667</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7.619047619047619</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.17906746031746</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>7.619047619047619</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.681175595238095</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.236979166666667</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="n">
+        <v>2.013936584249084</v>
       </c>
     </row>
     <row r="19">
@@ -1205,26 +1763,61 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.804878048780489</v>
+        <v>2212.698412698413</v>
       </c>
       <c r="D19" t="n">
-        <v>9.999753556600432</v>
+        <v>195.2332837241036</v>
       </c>
       <c r="E19" t="n">
-        <v>9.53950824679398</v>
+        <v>186.2475419612158</v>
       </c>
       <c r="F19" t="n">
         <v>1.048246230088551</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7294984448936291</v>
+        <v>0.7294984448936292</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6.19047619047619</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="n">
+        <v>1.156063988095238</v>
       </c>
     </row>
     <row r="20">
@@ -1235,25 +1828,63 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.649910767400357</v>
+        <v>2153.628117913832</v>
       </c>
       <c r="D20" t="n">
-        <v>9.876068949699402</v>
+        <v>192.8184890179407</v>
       </c>
       <c r="E20" t="n">
-        <v>9.387248707980644</v>
+        <v>183.2748557272411</v>
       </c>
       <c r="F20" t="n">
         <v>1.052072791179292</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7279192863162337</v>
+        <v>0.7279192863162338</v>
       </c>
       <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8147321428571428</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8.850446428571429</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.49156746031746</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>8.850446428571429</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.8147321428571428</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1265,17 +1896,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.566627007733493</v>
+        <v>2121.8820861678</v>
       </c>
       <c r="D21" t="n">
-        <v>9.945055002119483</v>
+        <v>194.1653595651899</v>
       </c>
       <c r="E21" t="n">
-        <v>9.324180768757332</v>
+        <v>182.043529294786</v>
       </c>
       <c r="F21" t="n">
         <v>1.066587537153132</v>
@@ -1284,6 +1915,36 @@
         <v>0.7072738603989598</v>
       </c>
       <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.7998511904761905</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.869791666666667</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.7998511904761905</v>
+      </c>
+      <c r="U21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1294,7 +1955,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
       </c>
     </row>
     <row r="23">
@@ -1317,6 +1978,38 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/25/Filled_2D_sections/axial/week25_axial_Batch_Allmarks.xlsx
+++ b/measurements/25/Filled_2D_sections/axial/week25_axial_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2015,4 +2221,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week25_axial_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2256.592970521541</v>
+      </c>
+      <c r="D10" t="n">
+        <v>57.47622250330056</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2121.8820861678</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2320.861678004535</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>235.7109043314344</v>
+      </c>
+      <c r="D11" t="n">
+        <v>39.64051036381492</v>
+      </c>
+      <c r="E11" t="n">
+        <v>192.8184890179407</v>
+      </c>
+      <c r="F11" t="n">
+        <v>293.5431836900257</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.165002747049296</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.152464277648165</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.034037504030065</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.426510047967435</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5479161629528073</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1611005169864732</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3319183006863793</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.742832489441156</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis2_s00_idx0104.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis2_s01_idx0106.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis2_s02_idx0108.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis2_s03_idx0110.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis2_s04_idx0112.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis2_s05_idx0114.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis2_s06_idx0116.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis2_s07_idx0118.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis2_s08_idx0120.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis2_s09_idx0122.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis2_s10_idx0123.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis2_s11_idx0125.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis2_s12_idx0127.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis2_s13_idx0129.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis2_s14_idx0131.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis2_s15_idx0133.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis2_s16_idx0135.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis2_s17_idx0137.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis2_s18_idx0139.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis2_s19_idx0140.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.6155870112510924</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.3077935056255462</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.7451598203705946</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.6386663736585051</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>18</v>
+      </c>
+      <c r="C48" t="n">
+        <v>17.71835730820106</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8.195682068688653</v>
+      </c>
+      <c r="E48" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="F48" t="n">
+        <v>28.63653273809524</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>43</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4.927239064230342</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.202368348804002</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.046875</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8.363095238095237</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>15</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.899553571428571</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.8649742724323386</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.7998511904761905</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.857142857142857</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>